--- a/data/trans_orig/Q5419_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar medios de transporte en 2023</t>
+          <t>Población según si es capaz de usar medios de transporte en 2023 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1031</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3682</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1031</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7501</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2291</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13602</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18771</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27223</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35580</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46640</t>
+          <t>46771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>39496</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66726</t>
+          <t>67088</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>83512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9811</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33451</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>64198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74678</t>
+          <t>74674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77134</t>
+          <t>76593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92649</t>
+          <t>92336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>144396</t>
+          <t>145094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>165746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18418</t>
+          <t>18784</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30340</t>
+          <t>29675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>549</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15983</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>48839</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>60439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>61274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101567</t>
+          <t>100610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118290</t>
+          <t>118342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19884</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9743</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10860</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58233</t>
+          <t>58695</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68333</t>
+          <t>68509</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71573</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82429</t>
+          <t>82518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134144</t>
+          <t>134013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>148829</t>
+          <t>149061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>361</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>425</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2176</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19457</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>41128</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49234</t>
+          <t>48969</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67402</t>
+          <t>67568</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77745</t>
+          <t>77512</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7869</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15774</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>16729</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>26269</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>38558</t>
+          <t>38622</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>346</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>533</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40751</t>
+          <t>40789</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>49708</t>
+          <t>49345</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32803</t>
+          <t>32660</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>76950</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>90194</t>
+          <t>89596</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>61848</t>
+          <t>60906</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62485</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>497</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>778</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7030</t>
+          <t>7540</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>906</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>329</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11341</t>
+          <t>11088</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>101289</t>
+          <t>100839</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>114001</t>
+          <t>113749</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>235277</t>
+          <t>238346</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>327342</t>
+          <t>329002</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>361542</t>
+          <t>361478</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>445193</t>
+          <t>443979</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>10160</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>25290</t>
+          <t>25445</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>41317</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>128350</t>
+          <t>128928</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>138832</t>
+          <t>139198</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>129509</t>
+          <t>129594</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>146868</t>
+          <t>147044</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>262508</t>
+          <t>261993</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>283741</t>
+          <t>282695</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>46664</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>114085</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>149081</t>
+          <t>150246</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18933</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>15054</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>42939</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>54610</t>
+          <t>54984</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>35366</t>
+          <t>31558</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>87168</t>
+          <t>86249</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>54243</t>
+          <t>58948</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>108177</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>21841</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>38737</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>96310</t>
+          <t>96229</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>122987</t>
+          <t>124225</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>532689</t>
+          <t>531928</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>561799</t>
+          <t>560778</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>702283</t>
+          <t>702232</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>892974</t>
+          <t>913384</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1261608</t>
+          <t>1263708</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1455890</t>
+          <t>1439393</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5419_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5419_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>13591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20295</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27073</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41672</t>
+          <t>47062</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>41038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46771</t>
+          <t>51896</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>33885</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>29649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39496</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>75557</t>
+          <t>82143</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67088</t>
+          <t>73139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>83512</t>
+          <t>89326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16383</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>17480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>11402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1741</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14505</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26662</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>36931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>13197</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15769</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>70302</t>
+          <t>77165</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64198</t>
+          <t>70531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74674</t>
+          <t>81925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>84701</t>
+          <t>87945</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76593</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92336</t>
+          <t>95942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>155004</t>
+          <t>165110</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145094</t>
+          <t>153242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165746</t>
+          <t>175274</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79850</t>
+          <t>87444</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>128464</t>
+          <t>134759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>208315</t>
+          <t>222203</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15401</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8883</t>
+          <t>9048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18784</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22892</t>
+          <t>22629</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17306</t>
+          <t>16868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29675</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5667</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8499</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15008</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11113</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15983</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>54413</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48839</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60439</t>
+          <t>59400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>54813</t>
+          <t>53106</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>46618</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61274</t>
+          <t>59469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>110031</t>
+          <t>107519</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100610</t>
+          <t>98376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>118342</t>
+          <t>115399</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,22 +2771,22 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19805</t>
+          <t>20542</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>664</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>16236</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>64463</t>
+          <t>72376</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>67227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68509</t>
+          <t>77105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71190</t>
+          <t>76715</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82518</t>
+          <t>88659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134013</t>
+          <t>147509</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149061</t>
+          <t>162429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>516</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>846</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,22 +3523,22 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>377</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>402</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1561</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>416</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10291</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7713</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10849</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19321</t>
+          <t>19228</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>19,61%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>27315</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>45660</t>
+          <t>47405</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>51404</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>76231</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>67568</t>
+          <t>70721</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77512</t>
+          <t>81364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11303</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>15652</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>21573</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>26628</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>32412</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27564</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -4248,22 +4248,22 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>344</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,17 +4318,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>407</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>268</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1775</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>675</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,17 +4544,17 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>45762</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>40993</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>49345</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>37771</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>32660</t>
+          <t>34391</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>44293</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>83533</t>
+          <t>84937</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>76950</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>89596</t>
+          <t>90700</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>66942</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>66942</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>64915</t>
+          <t>66942</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>125176</t>
+          <t>127166</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4226</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>26733</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>20049</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>60906</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>31716</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>29528</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62070</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13996</t>
+          <t>13704</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3798</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>12530</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>806</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11088</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12879</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>108507</t>
+          <t>133519</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>123994</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>113749</t>
+          <t>140063</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>300665</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>238346</t>
+          <t>106528</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>329002</t>
+          <t>126945</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>409172</t>
+          <t>250941</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>361478</t>
+          <t>237932</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>443979</t>
+          <t>262010</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>338151</t>
+          <t>163543</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>338151</t>
+          <t>163543</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>338151</t>
+          <t>163543</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>461405</t>
+          <t>314884</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>461405</t>
+          <t>314884</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>461405</t>
+          <t>314884</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,22 +5647,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,22 +5682,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -5725,17 +5725,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>13559</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>13817</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>19097</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>29166</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>49029</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>134501</t>
+          <t>148952</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>128928</t>
+          <t>141426</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>139198</t>
+          <t>153971</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>138650</t>
+          <t>156572</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>129594</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>167275</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>273152</t>
+          <t>305525</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>261993</t>
+          <t>292770</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>282695</t>
+          <t>316647</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,14%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>37333</t>
+          <t>40117</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>29539</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>47104</t>
+          <t>51922</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>88694</t>
+          <t>96110</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>43050</t>
+          <t>83400</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>116320</t>
+          <t>109932</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>126027</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>120194</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>152367</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>11952</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>18933</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>30360</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>42939</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>35467</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>56993</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>23102</t>
+          <t>24758</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>65888</t>
+          <t>71467</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>31558</t>
+          <t>60792</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>86249</t>
+          <t>85837</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>96225</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>58948</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>108177</t>
+          <t>112258</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>30452</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>37601</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>73464</t>
+          <t>81303</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>69719</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>96229</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>102658</t>
+          <t>111754</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>96804</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>124225</t>
+          <t>128613</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>547740</t>
+          <t>607887</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>531928</t>
+          <t>591632</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>560778</t>
+          <t>622981</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>773482</t>
+          <t>619555</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>702232</t>
+          <t>596836</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>913384</t>
+          <t>639596</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1321222</t>
+          <t>1227442</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1263708</t>
+          <t>1201172</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1439393</t>
+          <t>1254667</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>649320</t>
+          <t>715462</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>1031889</t>
+          <t>901182</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>1681209</t>
+          <t>1616644</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
